--- a/Scripts/Xlstojson/xlsx/Saamou - Cadeau.xlsx
+++ b/Scripts/Xlstojson/xlsx/Saamou - Cadeau.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\source\repos\SACEMGenerator\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\source\repos\SACEMGenerator\Scripts\Xlstojson\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D04AE2-8D53-4A22-BFE0-6B1259CFFC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB2A687-1C8F-4C1A-96F0-E829D4ED2047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="1560" windowWidth="20730" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1035" yWindow="-120" windowWidth="27885" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="154">
   <si>
     <t>Titre</t>
   </si>
@@ -479,6 +479,9 @@
   </si>
   <si>
     <t>GenreRepresentant</t>
+  </si>
+  <si>
+    <t>SAAMOU</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1062,9 @@
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
